--- a/test/Huy/excel/TC_Register_DecisionTable.xlsx
+++ b/test/Huy/excel/TC_Register_DecisionTable.xlsx
@@ -399,14 +399,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I20"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="45.83203125" customWidth="1"/>
-    <col min="5" max="5" width="25.83203125" customWidth="1"/>
-    <col min="6" max="6" width="25.83203125" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="21.83203125" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="51.83203125" customWidth="1"/>
+    <col min="5" max="5" width="21.83203125" customWidth="1"/>
+    <col min="6" max="6" width="21.83203125" customWidth="1"/>
     <col min="7" max="7" width="60.83203125" customWidth="1"/>
-    <col min="8" max="8" width="60.83203125" customWidth="1"/>
+    <col min="8" max="8" width="30.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -488,7 +488,7 @@
         <v>Abc@123456</v>
       </c>
       <c r="G3" t="str">
-        <v>Hiển thị lỗi dưới ô Họ tên: "Họ tên chỉ được chứa chữ cái và khoảng trắng"</v>
+        <v>"Họ tên chỉ được chứa chữ cái và khoảng trắng"</v>
       </c>
       <c r="H3" t="str">
         <v>TC_DT_02_result.png</v>
@@ -517,7 +517,7 @@
         <v>Abc@123456</v>
       </c>
       <c r="G4" t="str">
-        <v>Hiển thị lỗi: "Họ tên phải có ít nhất 3 ký tự."</v>
+        <v>"Họ tên phải có ít nhất 3 ký tự."</v>
       </c>
       <c r="H4" t="str">
         <v>TC_DT_03_result.png</v>
